--- a/data_raw/data_raw_2024_sheets/LTER1_BR_P04-09_2024.xlsx
+++ b/data_raw/data_raw_2024_sheets/LTER1_BR_P04-09_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/HLenihan 1/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryananderson/Reference/Bren/Coral Demography/data_raw/data_raw_2024_sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984692F0-AF42-EE4E-860C-16DFF7855841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7174D9FE-CD1A-EA48-A7D1-B50049BC5D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2960" yWindow="500" windowWidth="33320" windowHeight="23500" xr2:uid="{271AEECD-44A1-4440-BEF9-61486AD25B2D}"/>
+    <workbookView xWindow="0" yWindow="560" windowWidth="29920" windowHeight="18780" xr2:uid="{271AEECD-44A1-4440-BEF9-61486AD25B2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="40">
   <si>
     <t>LTER1</t>
   </si>
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t>Missing data</t>
-  </si>
-  <si>
-    <t>`</t>
   </si>
 </sst>
 </file>
@@ -223,16 +220,51 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF49900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color rgb="FFFFFFFF"/>
         <name val="Calibri"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -244,7 +276,79 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
+          <bgColor rgb="FFA1BCD6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFA52A2A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFB0006"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF006400"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF17A43F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB07EDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF159FEC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -275,21 +379,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFD4A6FF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFF49900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -315,116 +412,6 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF159FEC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF17A43F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF006400"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFB0006"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFA52A2A"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFA1BCD6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFB07EDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD4A6FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF49900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -438,20 +425,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF49900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -785,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{213B9055-DEAC-F842-8D18-63A0CDCE6C3B}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.1640625" customWidth="1"/>
@@ -1922,7 +1895,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>0</v>
       </c>
@@ -1960,7 +1933,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -1995,7 +1968,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -2030,7 +2003,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -2065,7 +2038,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -2100,7 +2073,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -2135,7 +2108,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -2170,7 +2143,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>0</v>
       </c>
@@ -2205,93 +2178,80 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="O41" t="s">
-        <v>40</v>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="A30:G40">
+    <cfRule type="expression" dxfId="20" priority="1">
+      <formula>A30="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>A30="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A2:H2">
-    <cfRule type="beginsWith" dxfId="22" priority="12" operator="beginsWith" text="FI">
+    <cfRule type="beginsWith" dxfId="18" priority="12" operator="beginsWith" text="FI">
       <formula>LEFT(A2,LEN("FI"))="FI"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="13" operator="containsText" text="Missing data">
+    <cfRule type="containsText" dxfId="17" priority="13" operator="containsText" text="Missing data">
       <formula>NOT(ISERROR(SEARCH("Missing data",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:H29 I3:K8 I10:K10 I17:K18 C30:G40 I20:K40">
-    <cfRule type="expression" dxfId="20" priority="14">
+  <conditionalFormatting sqref="A2:M2">
+    <cfRule type="beginsWith" dxfId="16" priority="5" operator="beginsWith" text="UK">
+      <formula>LEFT(A2,LEN("UK"))="UK"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="15" priority="11" operator="beginsWith" text="FU">
+      <formula>LEFT(A2,LEN("FU"))="FU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:K8 A3:H29 I10:K10 I17:K18 I20:K40">
+    <cfRule type="expression" dxfId="14" priority="14">
       <formula>A3="UK"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="15">
+    <cfRule type="expression" dxfId="13" priority="15">
       <formula>A3="Na"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:M2">
-    <cfRule type="beginsWith" dxfId="18" priority="5" operator="beginsWith" text="UK">
-      <formula>LEFT(A2,LEN("UK"))="UK"</formula>
+  <conditionalFormatting sqref="I3:K8 H3:H29 I10:K10 I17:K18 I20:K39 J40:K40">
+    <cfRule type="expression" dxfId="12" priority="23">
+      <formula>H3="Recruitment"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="17" priority="11" operator="beginsWith" text="FU">
-      <formula>LEFT(A2,LEN("FU"))="FU"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H29 I3:K8 I10:K10 I17:K18 I20:K39 J40:K40">
-    <cfRule type="containsText" dxfId="16" priority="16" operator="containsText" text=",">
-      <formula>NOT(ISERROR(SEARCH(",", H3)))</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="15" priority="17" operator="beginsWith" text="Fusion">
+    <cfRule type="beginsWith" dxfId="11" priority="17" operator="beginsWith" text="Fusion">
       <formula>LEFT(H3,LEN("Fusion"))="Fusion"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="14" priority="18" operator="beginsWith" text="Fission">
-      <formula>LEFT(H3,LEN("Fission"))="Fission"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="19">
-      <formula>H3="Missing Data"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="20">
-      <formula>H3="Death"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="21">
-      <formula>H3="Shrinkage"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="22">
       <formula>H3="Growth"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="23">
-      <formula>H3="Recruitment"</formula>
+    <cfRule type="expression" dxfId="9" priority="21">
+      <formula>H3="Shrinkage"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="20">
+      <formula>H3="Death"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="19">
+      <formula>H3="Missing Data"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="6" priority="18" operator="beginsWith" text="Fission">
+      <formula>LEFT(H3,LEN("Fission"))="Fission"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="16" operator="containsText" text=",">
+      <formula>NOT(ISERROR(SEARCH(",", H3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="beginsWith" dxfId="8" priority="6" operator="beginsWith" text="FI">
-      <formula>LEFT(I2,LEN("FI"))="FI"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="Missing data">
-      <formula>NOT(ISERROR(SEARCH("Missing data",I2)))</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="6" priority="8" operator="beginsWith" text="R">
-      <formula>LEFT(I2,LEN("R"))="R"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="NA">
-      <formula>NOT(ISERROR(SEARCH("NA",I2)))</formula>
-    </cfRule>
     <cfRule type="containsText" dxfId="4" priority="10" operator="containsText" text="D">
       <formula>NOT(ISERROR(SEARCH("D",I2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30:B37">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>A30="UK"</formula>
+    <cfRule type="beginsWith" dxfId="3" priority="6" operator="beginsWith" text="FI">
+      <formula>LEFT(I2,LEN("FI"))="FI"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
-      <formula>A30="Na"</formula>
+    <cfRule type="containsText" dxfId="2" priority="9" operator="containsText" text="NA">
+      <formula>NOT(ISERROR(SEARCH("NA",I2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A38:B40">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>A38="UK"</formula>
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="Missing data">
+      <formula>NOT(ISERROR(SEARCH("Missing data",I2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>A38="Na"</formula>
+    <cfRule type="beginsWith" dxfId="0" priority="8" operator="beginsWith" text="R">
+      <formula>LEFT(I2,LEN("R"))="R"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions gridLines="1"/>
